--- a/public/Managed_ET.xlsx
+++ b/public/Managed_ET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\iwmi_web_dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB0B2126-9268-40E9-9243-2F629657C454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8578006-AAF8-4CB7-BE59-92CB8F169F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{83A4F74E-3FB1-46EB-A7D1-F65CF80998B7}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{83A4F74E-3FB1-46EB-A7D1-F65CF80998B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
